--- a/data/final/series/comexstat_acucares_cana_exp_fob.xlsx
+++ b/data/final/series/comexstat_acucares_cana_exp_fob.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,7 +1013,7 @@
         <v>46053</v>
       </c>
       <c r="B74" t="n">
-        <v>619967622</v>
+        <v>621313185</v>
       </c>
     </row>
     <row r="75">
@@ -1021,7 +1021,7 @@
         <v>46081</v>
       </c>
       <c r="B75" t="n">
-        <v>713726654</v>
+        <v>717030066</v>
       </c>
     </row>
     <row r="76">
@@ -1029,7 +1029,7 @@
         <v>46112</v>
       </c>
       <c r="B76" t="n">
-        <v>543861591</v>
+        <v>545703069</v>
       </c>
     </row>
     <row r="77">
@@ -1037,7 +1037,7 @@
         <v>46142</v>
       </c>
       <c r="B77" t="n">
-        <v>344673367</v>
+        <v>346153809</v>
       </c>
     </row>
     <row r="78">
@@ -1045,7 +1045,7 @@
         <v>46173</v>
       </c>
       <c r="B78" t="n">
-        <v>617450435</v>
+        <v>620395097</v>
       </c>
     </row>
     <row r="79">
@@ -1053,7 +1053,7 @@
         <v>46203</v>
       </c>
       <c r="B79" t="n">
-        <v>938953227</v>
+        <v>950478133</v>
       </c>
     </row>
     <row r="80">
@@ -1061,7 +1061,7 @@
         <v>46234</v>
       </c>
       <c r="B80" t="n">
-        <v>844057652</v>
+        <v>846757948</v>
       </c>
     </row>
     <row r="81">
@@ -1069,7 +1069,15 @@
         <v>46265</v>
       </c>
       <c r="B81" t="n">
-        <v>753147930</v>
+        <v>752297715</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B82" t="n">
+        <v>809708916</v>
       </c>
     </row>
   </sheetData>
